--- a/tool/kintone-resourse-generator/template/class-space.xlsx
+++ b/tool/kintone-resourse-generator/template/class-space.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\kintone-resourse-generator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4A2928-AD4E-427D-B174-D5FC1736E9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE4F97C-C387-43D6-B2F4-DC5289D3F078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="space-settings" sheetId="1" r:id="rId1"/>
@@ -24,10 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
-  <si>
-    <t>スペース名</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="33">
   <si>
     <t>管理者</t>
   </si>
@@ -81,9 +78,6 @@
   </si>
   <si>
     <t>作成者</t>
-  </si>
-  <si>
-    <t>講座名 in ("{configName}")</t>
   </si>
   <si>
     <t>ユニバ事務局</t>
@@ -104,15 +98,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>クラススペース{PH}</t>
-  </si>
-  <si>
-    <t>勤怠管理{PH}</t>
-  </si>
-  <si>
-    <t>ファイル管理{PH}</t>
-  </si>
-  <si>
     <t>参加メンバーだけにこのスペースを公開する</t>
   </si>
   <si>
@@ -129,13 +114,49 @@
   </si>
   <si>
     <t>ユーザー／組織／グループ</t>
+  </si>
+  <si>
+    <t>種別</t>
+  </si>
+  <si>
+    <t>ユーザー</t>
+  </si>
+  <si>
+    <t>グループ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>講座名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in ("{configName}")</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファイル管理</t>
+  </si>
+  <si>
+    <t>勤怠管理</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -161,6 +182,18 @@
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -189,12 +222,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -509,36 +544,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="68.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="57.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="b">
+        <v>1</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
@@ -547,9 +578,6 @@
         <v>1</v>
       </c>
       <c r="D2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -561,55 +589,68 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.21875" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="b">
-        <v>1</v>
-      </c>
-      <c r="C2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="b">
-        <v>0</v>
-      </c>
-      <c r="C3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="b">
-        <v>0</v>
-      </c>
       <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -629,17 +670,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -650,54 +691,58 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.21875" customWidth="1"/>
-    <col min="2" max="2" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="13.21875" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" customWidth="1"/>
-    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" customWidth="1"/>
+    <col min="3" max="3" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="13.21875" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="B2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="b">
-        <v>1</v>
-      </c>
       <c r="D2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -711,16 +756,19 @@
       <c r="H2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" t="b">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -737,22 +785,25 @@
       <c r="H3" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="b">
-        <v>1</v>
+        <v>32</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
@@ -763,16 +814,19 @@
       <c r="H4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" t="b">
-        <v>1</v>
+        <v>32</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -787,6 +841,9 @@
         <v>1</v>
       </c>
       <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -798,74 +855,81 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.21875" customWidth="1"/>
     <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="9.109375" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" customWidth="1"/>
+    <col min="4" max="4" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="9.109375" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
+      <c r="B3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -874,6 +938,9 @@
         <v>1</v>
       </c>
       <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tool/kintone-resourse-generator/template/class-space.xlsx
+++ b/tool/kintone-resourse-generator/template/class-space.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\kintone-resourse-generator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE4F97C-C387-43D6-B2F4-DC5289D3F078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094791F5-64B9-49F4-9F0D-6B640CF2C496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="space-settings" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
   <si>
     <t>管理者</t>
   </si>
@@ -32,9 +32,6 @@
     <t>下位組織も含める</t>
   </si>
   <si>
-    <t>運営チーム</t>
-  </si>
-  <si>
     <t>アプリ名</t>
   </si>
   <si>
@@ -77,27 +74,6 @@
     <t/>
   </si>
   <si>
-    <t>作成者</t>
-  </si>
-  <si>
-    <t>ユニバ事務局</t>
-    <rPh sb="3" eb="6">
-      <t>ジムキョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>受講生</t>
-    <rPh sb="0" eb="3">
-      <t>ジュコウセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ggggggggggggg</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>参加メンバーだけにこのスペースを公開する</t>
   </si>
   <si>
@@ -119,73 +95,26 @@
     <t>種別</t>
   </si>
   <si>
-    <t>ユーザー</t>
+    <t>ファイル管理</t>
+  </si>
+  <si>
+    <t>勤怠管理</t>
   </si>
   <si>
     <t>グループ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>講座名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> in ("{configName}")</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ファイル管理</t>
-  </si>
-  <si>
-    <t>勤怠管理</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="ＭＳ ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -222,14 +151,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -555,16 +480,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -589,7 +514,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -600,58 +525,30 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>18</v>
+      <c r="B2" t="s">
+        <v>9</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -670,17 +567,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -691,7 +588,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.21875" customWidth="1"/>
@@ -704,42 +601,42 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
@@ -762,13 +659,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -777,74 +674,16 @@
         <v>1</v>
       </c>
       <c r="F3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -868,42 +707,42 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>29</v>
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -920,16 +759,14 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s">
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>

--- a/tool/kintone-resourse-generator/template/class-space.xlsx
+++ b/tool/kintone-resourse-generator/template/class-space.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\kintone-resourse-generator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094791F5-64B9-49F4-9F0D-6B640CF2C496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D8AB3D-E45C-4CC5-AC79-790438F3910D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>管理者</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>グループ</t>
+  </si>
+  <si>
+    <t>ファイル書き出し</t>
   </si>
 </sst>
 </file>
@@ -545,9 +548,6 @@
         <v>9</v>
       </c>
       <c r="C2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -588,18 +588,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.21875" customWidth="1"/>
     <col min="2" max="2" width="13.21875" customWidth="1"/>
     <col min="3" max="3" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="13.21875" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="4" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -627,8 +627,11 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>23</v>
       </c>
@@ -656,8 +659,11 @@
       <c r="I2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -683,6 +689,9 @@
         <v>0</v>
       </c>
       <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
         <v>0</v>
       </c>
     </row>

--- a/tool/kintone-resourse-generator/template/class-space.xlsx
+++ b/tool/kintone-resourse-generator/template/class-space.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\kintone-resourse-generator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D8AB3D-E45C-4CC5-AC79-790438F3910D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922316E2-88CC-4597-A9AF-59D7A840B825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="space-settings" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
   <si>
     <t>管理者</t>
   </si>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>削除</t>
-  </si>
-  <si>
-    <t>アクセス権の継承</t>
   </si>
   <si>
     <t/>
@@ -483,16 +480,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -528,10 +525,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -542,7 +539,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -572,12 +569,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -604,10 +601,10 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -628,15 +625,15 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -665,10 +662,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
         <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -703,7 +700,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.21875" customWidth="1"/>
@@ -711,10 +708,9 @@
     <col min="3" max="3" width="13.21875" customWidth="1"/>
     <col min="4" max="4" width="27.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9.109375" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -722,10 +718,10 @@
         <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>11</v>
@@ -736,19 +732,16 @@
       <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -762,17 +755,14 @@
       <c r="G2" t="b">
         <v>1</v>
       </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -784,9 +774,6 @@
         <v>1</v>
       </c>
       <c r="G3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" t="b">
         <v>1</v>
       </c>
     </row>
